--- a/server/scripts/samples/bulk-fornecedores.xlsx
+++ b/server/scripts/samples/bulk-fornecedores.xlsx
@@ -415,28 +415,28 @@
         <v>cnpj</v>
       </c>
       <c r="B1" t="str">
-        <v>name</v>
+        <v>nome</v>
       </c>
       <c r="C1" t="str">
         <v>email</v>
       </c>
       <c r="D1" t="str">
-        <v>phone</v>
+        <v>telefone</v>
       </c>
       <c r="E1" t="str">
-        <v>pixKey</v>
+        <v>pix</v>
       </c>
       <c r="F1" t="str">
-        <v>bankCode</v>
+        <v>banco</v>
       </c>
       <c r="G1" t="str">
-        <v>agency</v>
+        <v>agencia</v>
       </c>
       <c r="H1" t="str">
-        <v>account</v>
+        <v>conta</v>
       </c>
       <c r="I1" t="str">
-        <v>notes</v>
+        <v>observacoes</v>
       </c>
     </row>
     <row r="2">
